--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.74978036936924</v>
+        <v>6.784339310022502</v>
       </c>
       <c r="D2" t="n">
-        <v>54.99552329844463</v>
+        <v>8.936772535997253</v>
       </c>
       <c r="E2" t="n">
-        <v>8.484005485306124</v>
+        <v>1.378650891362245</v>
       </c>
       <c r="F2" t="n">
-        <v>16.84729174077927</v>
+        <v>2.737684907876631</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.25930606703649</v>
+        <v>3.77963723589343</v>
       </c>
       <c r="D3" t="n">
-        <v>8.860022573334675</v>
+        <v>1.439753668166885</v>
       </c>
       <c r="E3" t="n">
-        <v>8.484005485306124</v>
+        <v>1.378650891362245</v>
       </c>
       <c r="F3" t="n">
-        <v>16.84729174077927</v>
+        <v>2.737684907876631</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.49272574905842</v>
+        <v>3.167567934221993</v>
       </c>
       <c r="D4" t="n">
-        <v>41.50309220395171</v>
+        <v>6.744252483142153</v>
       </c>
       <c r="E4" t="n">
-        <v>8.484005485306124</v>
+        <v>1.378650891362245</v>
       </c>
       <c r="F4" t="n">
-        <v>16.84729174077927</v>
+        <v>2.737684907876631</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.83118270617898</v>
+        <v>4.197567189754084</v>
       </c>
       <c r="D5" t="n">
-        <v>31.47569280941842</v>
+        <v>5.114800081530492</v>
       </c>
       <c r="E5" t="n">
-        <v>8.484005485306124</v>
+        <v>1.378650891362245</v>
       </c>
       <c r="F5" t="n">
-        <v>16.84729174077927</v>
+        <v>2.737684907876631</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
